--- a/02-精益培训/03-培训计划/03-培训日程安排模板.xlsx
+++ b/02-精益培训/03-培训计划/03-培训日程安排模板.xlsx
@@ -92,7 +92,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -119,11 +119,20 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="001F3A5F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -147,6 +156,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -530,7 +540,13 @@
           <t>03-培训日程安排模板</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
+      <c r="D1" s="11" t="n"/>
+      <c r="E1" s="11" t="n"/>
+      <c r="F1" s="11" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -538,6 +554,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -545,6 +562,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
@@ -552,6 +570,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
@@ -559,6 +578,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -566,6 +586,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
@@ -573,6 +594,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -580,6 +602,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
@@ -587,6 +610,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
@@ -594,6 +618,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
@@ -601,6 +626,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
@@ -608,6 +634,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
@@ -615,6 +642,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
@@ -622,6 +650,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
@@ -629,6 +658,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
@@ -636,6 +666,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
@@ -643,6 +674,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
@@ -650,6 +682,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
@@ -657,6 +690,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
@@ -664,6 +698,7 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
@@ -699,6 +734,7 @@
         </is>
       </c>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
@@ -706,6 +742,7 @@
         </is>
       </c>
     </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
@@ -1395,7 +1432,7 @@
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>紧固件行业案例</t>
+          <t>制造业案例</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2366,7 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>选择紧固件行业案例</t>
+          <t>选择制造业案例</t>
         </is>
       </c>
     </row>
